--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rc8b64d9c37694b6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rc6e7dd7f72a94457"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Re6736e8101f6420d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Re296de677fd84cf5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rf174e13b41e24156"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R9c76debbbecd4ee4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rfeeb46df306c4b64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R9dd679cf3ce949ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rc4a2f8cfa2574ba7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R8b9d9d75c1384170"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -288,7 +288,7 @@
         <x:v>交付物名称</x:v>
       </x:c>
       <x:c r="B1" s="8" t="str">
-        <x:v>固定路径或命名规则</x:v>
+        <x:v>固定路径/命名规则</x:v>
       </x:c>
       <x:c r="C1" s="8" t="str">
         <x:v>用途</x:v>

--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R9c76debbbecd4ee4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rfeeb46df306c4b64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R9dd679cf3ce949ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rc4a2f8cfa2574ba7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R8b9d9d75c1384170"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R1f72500366d74c22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R9cfa70c70a0f4652"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R454747fa85654414"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Re28074cc9c5841f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Ree4380d36c7e4e9b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -425,10 +425,10 @@
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="5" t="str">
-        <x:v>交接摘要</x:v>
+        <x:v>发布摘要</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>output/results/handover.json</x:v>
+        <x:v>output/results/release-summary.json</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
         <x:v>记录职责边界和结果计数</x:v>
@@ -453,13 +453,13 @@
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="6" t="str">
-        <x:v>交接说明</x:v>
+        <x:v>发布说明</x:v>
       </x:c>
       <x:c r="B13" s="6" t="str">
-        <x:v>output/HANDOVER.md</x:v>
+        <x:v>output/RELEASE-NOTES.md</x:v>
       </x:c>
       <x:c r="C13" s="6" t="str">
-        <x:v>供现场管理员接手</x:v>
+        <x:v>供现场管理员执行发布</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
         <x:v>核对职责边界</x:v>
@@ -496,7 +496,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="str">
-        <x:v>交接摘要</x:v>
+        <x:v>发布摘要</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
         <x:v>status</x:v>
@@ -510,7 +510,7 @@
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="str">
-        <x:v>交接摘要</x:v>
+        <x:v>发布摘要</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
         <x:v>review_scope</x:v>
@@ -524,7 +524,7 @@
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>交接摘要</x:v>
+        <x:v>发布摘要</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
         <x:v>apply_owner</x:v>
@@ -712,7 +712,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="str">
-        <x:v>handover.json</x:v>
+        <x:v>release-summary.json</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
         <x:v>object_count</x:v>
@@ -729,7 +729,7 @@
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="str">
-        <x:v>handover.json</x:v>
+        <x:v>release-summary.json</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
         <x:v>rule_count</x:v>
@@ -746,7 +746,7 @@
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>handover.json</x:v>
+        <x:v>release-summary.json</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
         <x:v>binding_count</x:v>
@@ -763,7 +763,7 @@
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>handover.json</x:v>
+        <x:v>release-summary.json</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
         <x:v>resolved_risk_count</x:v>
@@ -899,7 +899,7 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
-        <x:v>交接说明</x:v>
+        <x:v>发布说明</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
         <x:v>段落与措辞可以变化</x:v>
